--- a/16_Crypto_Digital_Assets/instances/public_coinbase_2023.xlsx
+++ b/16_Crypto_Digital_Assets/instances/public_coinbase_2023.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -40,7 +40,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="285">
   <si>
-    <t xml:space="preserve">[TOKEN] — Crypto / Digital Asset Model</t>
+    <t xml:space="preserve">Coinbase 2023 custody and staking scale</t>
   </si>
   <si>
     <t xml:space="preserve">Protocol:</t>
@@ -1103,36 +1103,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1140,7 +1136,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1148,7 +1144,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1156,111 +1152,111 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1344,34 +1340,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1517,63 +1513,63 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1587,259 +1583,259 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="50"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="31" t="n">
         <f aca="false">'Supply Rollforward &amp; Unlocks'!E16-('Supply Rollforward &amp; Unlocks'!E5+'Supply Rollforward &amp; Unlocks'!E6+'Supply Rollforward &amp; Unlocks'!E7+'Supply Rollforward &amp; Unlocks'!E8-'Supply Rollforward &amp; Unlocks'!E9)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="32" t="str">
+      <c r="D5" s="31" t="str">
         <f aca="false">IF(ABS(C5)&lt;0.000001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="31" t="n">
         <f aca="false">'Supply Rollforward &amp; Unlocks'!E16-'Supply Rollforward &amp; Unlocks'!E10</f>
         <v>755</v>
       </c>
-      <c r="D6" s="32" t="str">
+      <c r="D6" s="31" t="str">
         <f aca="false">IF(C6&gt;=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="22" t="n">
         <f aca="false">'Supply Rollforward &amp; Unlocks'!E18</f>
         <v>0.03</v>
       </c>
-      <c r="D7" s="32" t="str">
+      <c r="D7" s="31" t="str">
         <f aca="false">IF(C7&lt;='Supply Rollforward &amp; Unlocks'!E11,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="22" t="n">
         <f aca="false">'Supply Rollforward &amp; Unlocks'!E19</f>
         <v>0.0134228187919463</v>
       </c>
-      <c r="D8" s="32" t="str">
+      <c r="D8" s="31" t="str">
         <f aca="false">IF(C8&lt;='Supply Rollforward &amp; Unlocks'!E12,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="32" t="str">
+      <c r="C9" s="31" t="str">
         <f aca="false">'Staking Yield'!C14</f>
         <v>-</v>
       </c>
-      <c r="D9" s="32" t="str">
+      <c r="D9" s="31" t="str">
         <f aca="false">IF(ISNUMBER(C9),IF(C9&gt;=0,"PASS","REVIEW"),"REVIEW")</f>
         <v>REVIEW</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="30" t="n">
         <f aca="false">'Treasury &amp; Runway'!D19</f>
         <v>20.5310091743119</v>
       </c>
-      <c r="D10" s="32" t="str">
+      <c r="D10" s="31" t="str">
         <f aca="false">IF(C10&gt;='Treasury &amp; Runway'!D12,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="0" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="27" t="n">
         <f aca="false">'Treasury &amp; Runway'!D20</f>
         <v>20.5310091743119</v>
       </c>
-      <c r="D11" s="32" t="str">
+      <c r="D11" s="31" t="str">
         <f aca="false">IF(C11&gt;='Treasury &amp; Runway'!D13,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="31" t="n">
         <f aca="false">COUNTIF('Custody &amp; Liquidity'!D5:D12,"&lt;&gt;PASS")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="32" t="str">
+      <c r="D12" s="31" t="str">
         <f aca="false">IF(C12=0,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="C13" s="32" t="n">
-        <f aca="false">IFERROR(Valuation!C12/Valuation!C11,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="32" t="str">
-        <f aca="false">IF(C13&lt;=2,"PASS",IF(C13&lt;=5,"REVIEW","BREACH"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="C13" s="31" t="str">
+        <f aca="false">IFERROR(Valuation!C12/Valuation!C11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D13" s="31" t="str">
+        <f aca="false">IF(ISNUMBER(C13),IF(C13&lt;=2,"PASS",IF(C13&lt;=5,"REVIEW","BREACH")),"REVIEW")</f>
+        <v>REVIEW</v>
+      </c>
+      <c r="E13" s="0" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C15" s="34" t="str">
+      <c r="C15" s="33" t="str">
         <f aca="false">IF(COUNTIF(D5:D13,"FAIL")+COUNTIF(D5:D13,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D13,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v>REVIEW</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="24" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="23" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="20" t="n">
         <f aca="false">'Supply Rollforward &amp; Unlocks'!E16</f>
         <v>1055</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="20" t="n">
         <f aca="false">'Supply Rollforward &amp; Unlocks'!E17</f>
         <v>755</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="22" t="n">
         <f aca="false">'Supply Rollforward &amp; Unlocks'!E18</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="26" t="n">
         <f aca="false">Valuation!C11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="26" t="n">
         <f aca="false">Valuation!C12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="C23" s="23" t="str">
+      <c r="C23" s="22" t="str">
         <f aca="false">'Staking Yield'!C14</f>
         <v>-</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="30" t="n">
         <f aca="false">'Treasury &amp; Runway'!D19</f>
         <v>20.5310091743119</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="27" t="n">
         <f aca="false">'Treasury &amp; Runway'!D20</f>
         <v>20.5310091743119</v>
       </c>
@@ -1847,7 +1843,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1861,104 +1857,104 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="24" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="23" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
+      <c r="C5" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="19" t="n">
         <v>16.8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C7" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
+      <c r="C7" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C8" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="24" t="s">
+      <c r="C8" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="23" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>249</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="20" t="n">
         <f aca="false">C5*Tokenomics!C12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="C12" s="23" t="str">
+      <c r="C12" s="22" t="str">
         <f aca="false">IFERROR(C6/C11,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="C13" s="23" t="str">
+      <c r="C13" s="22" t="str">
         <f aca="false">IFERROR(C7/(C11*C8),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
         <v>252</v>
       </c>
-      <c r="C14" s="35" t="str">
+      <c r="C14" s="34" t="str">
         <f aca="false">IFERROR(C13-C12,"-")</f>
         <v>-</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>253</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1972,249 +1968,249 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:I11"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="0" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="35" t="n">
         <f aca="false">Valuation!C11</f>
         <v>0</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="35" t="n">
         <f aca="false">Valuation!C12</f>
         <v>0</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="35" t="n">
         <f aca="false">Valuation!C6</f>
         <v>197.154</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="35" t="n">
         <f aca="false">Valuation!C8</f>
         <v>16.8</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="27" t="n">
         <f aca="false">IFERROR(C5/E5,"-")</f>
         <v>0</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="27" t="n">
         <f aca="false">IFERROR(D5/E5,"-")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="28" t="n">
+      <c r="I5" s="27" t="n">
         <f aca="false">IFERROR(C5/(F5*365),"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="37" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="28" t="str">
+      <c r="C6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="27" t="str">
         <f aca="false">IFERROR(C6/E6,"-")</f>
         <v>-</v>
       </c>
-      <c r="H6" s="28" t="str">
+      <c r="H6" s="27" t="str">
         <f aca="false">IFERROR(D6/E6,"-")</f>
         <v>-</v>
       </c>
-      <c r="I6" s="28" t="str">
+      <c r="I6" s="27" t="str">
         <f aca="false">IFERROR(C6/(F6*365),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="37" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="28" t="str">
+      <c r="C7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27" t="str">
         <f aca="false">IFERROR(C7/E7,"-")</f>
         <v>-</v>
       </c>
-      <c r="H7" s="28" t="str">
+      <c r="H7" s="27" t="str">
         <f aca="false">IFERROR(D7/E7,"-")</f>
         <v>-</v>
       </c>
-      <c r="I7" s="28" t="str">
+      <c r="I7" s="27" t="str">
         <f aca="false">IFERROR(C7/(F7*365),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="37" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="28" t="str">
+      <c r="C8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="27" t="str">
         <f aca="false">IFERROR(C8/E8,"-")</f>
         <v>-</v>
       </c>
-      <c r="H8" s="28" t="str">
+      <c r="H8" s="27" t="str">
         <f aca="false">IFERROR(D8/E8,"-")</f>
         <v>-</v>
       </c>
-      <c r="I8" s="28" t="str">
+      <c r="I8" s="27" t="str">
         <f aca="false">IFERROR(C8/(F8*365),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="37" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="28" t="str">
+      <c r="C9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27" t="str">
         <f aca="false">IFERROR(C9/E9,"-")</f>
         <v>-</v>
       </c>
-      <c r="H9" s="28" t="str">
+      <c r="H9" s="27" t="str">
         <f aca="false">IFERROR(D9/E9,"-")</f>
         <v>-</v>
       </c>
-      <c r="I9" s="28" t="str">
+      <c r="I9" s="27" t="str">
         <f aca="false">IFERROR(C9/(F9*365),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="37" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="28" t="str">
+      <c r="C10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="27" t="str">
         <f aca="false">IFERROR(C10/E10,"-")</f>
         <v>-</v>
       </c>
-      <c r="H10" s="28" t="str">
+      <c r="H10" s="27" t="str">
         <f aca="false">IFERROR(D10/E10,"-")</f>
         <v>-</v>
       </c>
-      <c r="I10" s="28" t="str">
+      <c r="I10" s="27" t="str">
         <f aca="false">IFERROR(C10/(F10*365),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="37" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28" t="str">
+      <c r="C11" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27" t="str">
         <f aca="false">IFERROR(C11/E11,"-")</f>
         <v>-</v>
       </c>
-      <c r="H11" s="28" t="str">
+      <c r="H11" s="27" t="str">
         <f aca="false">IFERROR(D11/E11,"-")</f>
         <v>-</v>
       </c>
-      <c r="I11" s="28" t="str">
+      <c r="I11" s="27" t="str">
         <f aca="false">IFERROR(C11/(F11*365),"-")</f>
         <v>-</v>
       </c>
@@ -2222,7 +2218,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2236,131 +2232,131 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G10"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
         <v>265</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="12" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="39" t="n">
+      <c r="C7" s="38" t="n">
         <f aca="false">Tokenomics!C12</f>
         <v>0</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">MIN(Tokenomics!$C$10,C7+Tokenomics!$C$10*$C$4)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">MIN(Tokenomics!$C$10,D7+Tokenomics!$C$10*$C$4)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="20" t="n">
         <f aca="false">MIN(Tokenomics!$C$10,E7+Tokenomics!$C$10*$C$4)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="20" t="n">
         <f aca="false">MIN(Tokenomics!$C$10,F7+Tokenomics!$C$10*$C$4)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>272</v>
       </c>
-      <c r="C8" s="23" t="str">
+      <c r="C8" s="22" t="str">
         <f aca="false">IFERROR(1-$C$7/C7,"-")</f>
         <v>-</v>
       </c>
-      <c r="D8" s="23" t="str">
+      <c r="D8" s="22" t="str">
         <f aca="false">IFERROR(1-$C$7/D7,"-")</f>
         <v>-</v>
       </c>
-      <c r="E8" s="23" t="str">
+      <c r="E8" s="22" t="str">
         <f aca="false">IFERROR(1-$C$7/E7,"-")</f>
         <v>-</v>
       </c>
-      <c r="F8" s="23" t="str">
+      <c r="F8" s="22" t="str">
         <f aca="false">IFERROR(1-$C$7/F7,"-")</f>
         <v>-</v>
       </c>
-      <c r="G8" s="23" t="str">
+      <c r="G8" s="22" t="str">
         <f aca="false">IFERROR(1-$C$7/G7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>273</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">Valuation!$C$5*C7</f>
         <v>0</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">Valuation!$C$5*D7</f>
         <v>0</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">Valuation!$C$5*E7</f>
         <v>0</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">Valuation!$C$5*F7</f>
         <v>0</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">Valuation!$C$5*G7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="15" t="s">
         <v>274</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2374,121 +2370,121 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="32" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="31" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2502,638 +2498,638 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F63"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="9" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="1" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="1" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="9" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="10" t="s">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="1" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="1" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="1" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="1" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="9" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="10" t="s">
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="1" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="1" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="1" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="1" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="1" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="9" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="10" t="s">
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="1" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="1" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="1" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="1" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="1" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="9" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="10" t="s">
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="1" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="0" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="1" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="0" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3183,7 +3179,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3197,230 +3193,230 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I54"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H23" s="11"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H39" s="11"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H41" s="11"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H42" s="11"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H43" s="11"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H44" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H46" s="11"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H47" s="11"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H48" s="11"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H49" s="11"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H50" s="11"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H51" s="11"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H52" s="11"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H53" s="11"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H54" s="11"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="10"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="10"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="10"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="10"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="10"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="10"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="10"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="10"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="10"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="10"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H52" s="10"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="10"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3438,7 +3434,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3452,212 +3448,212 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J29" s="11"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J40" s="11"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3671,7 +3667,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3685,149 +3681,149 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:F13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="0" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="str">
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="str">
         <f aca="false">IFERROR(C5/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15" t="str">
+      <c r="C6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="str">
         <f aca="false">IFERROR(C6/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15" t="str">
+      <c r="C7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="str">
         <f aca="false">IFERROR(C7/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15" t="str">
+      <c r="C8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="str">
         <f aca="false">IFERROR(C8/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15" t="str">
+      <c r="C9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="str">
         <f aca="false">IFERROR(C9/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="16" t="n">
         <f aca="false">SUM(C5:C9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="s">
+      <c r="C12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="15" t="str">
+      <c r="C13" s="14" t="str">
         <f aca="false">IFERROR(C12/C10,"-")</f>
         <v>-</v>
       </c>
@@ -3835,7 +3831,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3849,256 +3845,256 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F23"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="20" t="n">
         <f aca="false">IF($C$3="Downside",D5,C5)</f>
         <v>1000</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="0" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">IF($C$3="Downside",D6,C6)</f>
         <v>20</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="0" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="19" t="n">
         <v>250</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">IF($C$3="Downside",D7,C7)</f>
         <v>30</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="0" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">IF($C$3="Downside",D8,C8)</f>
         <v>10</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="0" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="21" t="n">
+      <c r="D9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20" t="n">
         <f aca="false">IF($C$3="Downside",D9,C9)</f>
         <v>5</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="0" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">IF($C$3="Downside",D10,C10)</f>
         <v>300</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="0" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="22" t="n">
         <f aca="false">IF($C$3="Downside",D11,C11)</f>
         <v>0.1</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="0" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="22" t="n">
         <f aca="false">IF($C$3="Downside",D12,C12)</f>
         <v>0.08</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="0" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="24" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="23" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="20" t="n">
         <f aca="false">E5+E6+E7+E8-E9</f>
         <v>1055</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="20" t="n">
         <f aca="false">E16-E10</f>
         <v>755</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="22" t="n">
         <f aca="false">IFERROR(E7/E5,0)</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="22" t="n">
         <f aca="false">IFERROR(E8/MAX(E17-E8,0.000001),0)</f>
         <v>0.0134228187919463</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="22" t="n">
         <f aca="false">IFERROR(E10/E16,0)</f>
         <v>0.28436018957346</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="22" t="n">
         <f aca="false">IFERROR(E16/E5-1,0)</f>
         <v>0.0549999999999999</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="15" t="s">
         <v>154</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4112,122 +4108,122 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D16"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="24" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="23" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
+      <c r="C5" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="25" t="n">
         <v>197.154</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="25" t="n">
         <v>4.571</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="25" t="n">
         <v>16.8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="24" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="23" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="26" t="n">
         <f aca="false">C5*Tokenomics!C12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="26" t="n">
         <f aca="false">C5*Tokenomics!C10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="27" t="n">
         <f aca="false">IFERROR(C11/C6,"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="27" t="n">
         <f aca="false">IFERROR(C12/C6,"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="27" t="n">
         <f aca="false">IFERROR(C11/C7,"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="27" t="n">
         <f aca="false">IFERROR(C11/(C8*365),"-")</f>
         <v>0</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>168</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4241,258 +4237,258 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E24"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="25" t="n">
         <v>5139</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="25" t="n">
         <v>5139</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="25" t="n">
         <v>700</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="25" t="n">
         <v>700</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="25" t="n">
         <v>272.5</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="25" t="n">
         <v>272.5</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="0" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="25" t="n">
         <v>272.5</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="25" t="n">
         <v>272.5</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="28" t="n">
         <v>18</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="28" t="n">
         <v>18</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="29" t="n">
         <v>1.25</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="29" t="n">
         <v>1.25</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="0" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="21" t="n">
         <v>0.35</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="0" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="21" t="n">
         <v>0.35</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="21" t="n">
         <v>0.65</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="0" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="26" t="n">
         <f aca="false">C5+C6*(1-C14)+C8*(1-C15)</f>
         <v>5740.5</v>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="D18" s="26" t="n">
         <f aca="false">D5+D6*(1-D14)+D8*(1-D15)</f>
         <v>5594.7</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="30" t="n">
         <f aca="false">IFERROR(C18/C10,0)</f>
         <v>21.0660550458716</v>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="30" t="n">
         <f aca="false">IFERROR(D18/D10,0)</f>
         <v>20.5310091743119</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="27" t="n">
         <f aca="false">IFERROR(C18/C11,0)</f>
         <v>21.0660550458716</v>
       </c>
-      <c r="D20" s="28" t="n">
+      <c r="D20" s="27" t="n">
         <f aca="false">IFERROR(D18/D11,0)</f>
         <v>20.5310091743119</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="22" t="n">
         <f aca="false">IFERROR(C7/SUM(C5:C9),0)</f>
         <v>0.0134476382585308</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="22" t="n">
         <f aca="false">IFERROR(D7/SUM(D5:D9),0)</f>
         <v>0.00340078217990138</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="C22" s="32" t="str">
+      <c r="C22" s="31" t="str">
         <f aca="false">IF(AND(D19&gt;=D12,D20&gt;=D13),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="D22" s="32"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16" t="s">
+      <c r="D22" s="31"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="15" t="s">
         <v>198</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4506,162 +4502,162 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="50"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="32" t="str">
+      <c r="D5" s="31" t="str">
         <f aca="false">IF(C5=1,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="32" t="str">
+      <c r="D6" s="31" t="str">
         <f aca="false">IF(C6=1,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="32" t="str">
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="31" t="str">
         <f aca="false">IF(C7=0,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="D8" s="32" t="str">
+      <c r="D8" s="31" t="str">
         <f aca="false">IF(C8&lt;=0.4,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="32" t="str">
+      <c r="D9" s="31" t="str">
         <f aca="false">IF(C9&lt;=10,"PASS",IF(C9&lt;=25,"REVIEW","BREACH"))</f>
         <v>PASS</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="D10" s="32" t="str">
+      <c r="D10" s="31" t="str">
         <f aca="false">IF(C10&lt;=0.35,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="0" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.3</v>
       </c>
-      <c r="D11" s="32" t="str">
+      <c r="D11" s="31" t="str">
         <f aca="false">IF(C11&lt;=0.5,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="32" t="str">
+      <c r="C12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="31" t="str">
         <f aca="false">IF(C12=0,"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="15" t="s">
         <v>219</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
